--- a/ONCHO/Entomological survey Survey/Nigeria/2024/taraba/sept24/ng_oncho_2410_4_b_flies_lab_tar.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2024/taraba/sept24/ng_oncho_2410_4_b_flies_lab_tar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2024\taraba\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2024\taraba\sept24\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A718BCE0-07AB-46D4-A707-B5EFB97F9344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EDF1E4-8178-4B05-8B08-1A3478E67D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -765,9 +765,6 @@
     <t>pools_pos</t>
   </si>
   <si>
-    <t>pools_pos_details_tar</t>
-  </si>
-  <si>
     <t>${pools_pos} &gt; 0</t>
   </si>
   <si>
@@ -795,9 +792,6 @@
     <t>pools_neg</t>
   </si>
   <si>
-    <t>pools_neg_details_tar</t>
-  </si>
-  <si>
     <t>${pools_neg} &gt; 0</t>
   </si>
   <si>
@@ -825,9 +819,6 @@
     <t>pools_l_100</t>
   </si>
   <si>
-    <t>pools_l_100_details_tar</t>
-  </si>
-  <si>
     <t>${pools_l_100} &gt; 0</t>
   </si>
   <si>
@@ -843,10 +834,19 @@
     <t>Test type for pool **${pools_l_100_name}**</t>
   </si>
   <si>
-    <t>ng_oncho_2410_4_b_flies_lab_tar_v2</t>
-  </si>
-  <si>
-    <t>(Taraba) 4. Blackfly Lab App V2</t>
+    <t>ng_oncho_2410_4_b_flies_lab_tar_v3</t>
+  </si>
+  <si>
+    <t>(Taraba) 4. Blackfly Lab App V3</t>
+  </si>
+  <si>
+    <t>pools_pos_d_tar</t>
+  </si>
+  <si>
+    <t>pools_neg_d_tar</t>
+  </si>
+  <si>
+    <t>pools_l_100_d_tar</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1662,7 @@
         <v>76</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>86</v>
@@ -1672,7 +1672,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="20"/>
       <c r="H11" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
@@ -1680,7 +1680,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="18"/>
       <c r="N11" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -1688,7 +1688,7 @@
         <v>93</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>88</v>
@@ -1710,7 +1710,7 @@
         <v>93</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>89</v>
@@ -1734,7 +1734,7 @@
         <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>90</v>
@@ -1758,10 +1758,10 @@
         <v>111</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="7"/>
@@ -1798,7 +1798,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>101</v>
@@ -1820,7 +1820,7 @@
         <v>76</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>87</v>
@@ -1830,7 +1830,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="20"/>
       <c r="H18" s="18" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I18" s="18"/>
       <c r="J18" s="18"/>
@@ -1838,7 +1838,7 @@
       <c r="L18" s="21"/>
       <c r="M18" s="18"/>
       <c r="N18" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -1846,7 +1846,7 @@
         <v>93</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>88</v>
@@ -1868,7 +1868,7 @@
         <v>93</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>89</v>
@@ -1892,7 +1892,7 @@
         <v>93</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>90</v>
@@ -1916,10 +1916,10 @@
         <v>111</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="7"/>
@@ -1956,7 +1956,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>47</v>
@@ -1978,7 +1978,7 @@
         <v>76</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>92</v>
@@ -1988,7 +1988,7 @@
       <c r="F25" s="18"/>
       <c r="G25" s="20"/>
       <c r="H25" s="18" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
@@ -1996,7 +1996,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="18"/>
       <c r="N25" s="21" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:14" s="10" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
@@ -2004,7 +2004,7 @@
         <v>93</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>88</v>
@@ -2026,10 +2026,10 @@
         <v>111</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="7"/>
@@ -2159,7 +2159,7 @@
       <c r="G33" s="9"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -2179,7 +2179,7 @@
       <c r="G34" s="9"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>20</v>
